--- a/קבצים/התקבל/זמנים בין שלבים.xlsx
+++ b/קבצים/התקבל/זמנים בין שלבים.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="זמנים בין שלבים" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="השפעת הסינון" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +21,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,6 +33,10 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="4">
@@ -78,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -91,6 +96,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1957,4 +1966,265 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>הסינון שבשימוש: 1.5 סטיות תקן, קנה מידה log, חוסם low. תצפית מחוץ לחלון אינה נספרת - לא בזמנים ולא בשיעור ההגעה.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="4" ht="40" customHeight="1">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>שלב</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>רצפת החלון (ימים)</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>תצפיות לפני</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>נפסלו כמהיר מדי</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>תצפיות אחרי</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>שיעור גיוס אחרי הסינון</t>
+        </is>
+      </c>
+      <c r="G4" s="1" t="inlineStr">
+        <is>
+          <t>חציון ימים אחרי</t>
+        </is>
+      </c>
+      <c r="H4" s="1" t="inlineStr">
+        <is>
+          <t>ממוצע ימים אחרי</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>בדיקת קבצים</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>1170</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>181</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>989</v>
+      </c>
+      <c r="F5" s="9" t="n">
+        <v>0.08397300000000001</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>79</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>84.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>זימון למבחן מקוון</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>551</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>517</v>
+      </c>
+      <c r="F6" s="9" t="n">
+        <v>0.170064</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>91</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>95.3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>יום מיון מקוון</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>654</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>615</v>
+      </c>
+      <c r="F7" s="9" t="n">
+        <v>0.217876</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>69</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>76.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>יום מיון</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>897</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>846</v>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>0.398507</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>57</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>65.59999999999999</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>מרכז הערכה</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>487</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>456</v>
+      </c>
+      <c r="F9" s="9" t="n">
+        <v>0.470669</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>42.4</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>יחב"מ</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>1565</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>1415</v>
+      </c>
+      <c r="F10" s="9" t="n">
+        <v>0.704804</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>27.9</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>למה החלון מחושב על הלוג ולא על הימים עצמם: התפלגות זמנים חסומה באפס ומשתרעת ימינה. בקנה מידה רגיל, «ממוצע פחות 1.5 סטיות תקן» יוצא שלילי בחלק מהמעברים - ואז הוא אינו חוסם דבר בקצה המהיר, שהוא בדיוק הקצה שבו הבעיה. הגיליון הראשון מציג את שני החלונות זה לצד זה, והגבולות השליליים מסומנים שם בצהוב.
+למה נחסם רק הקצה המהיר: בקצה האיטי אין ממצא דומה, ולבדיקת קבצים נפסלות שם אפס תצפיות. חסימה דו-צדדית היתה מוחקת גיוסים איטיים אמיתיים בשלבים המאוחרים ומושכת את הזמן הממוצע כלפי מטה - כלומר גורמת למחשבון להבטיח גיוס מהיר מהמציאות.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:H2"/>
+    <mergeCell ref="A13:H20"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/קבצים/התקבל/זמנים בין שלבים.xlsx
+++ b/קבצים/התקבל/זמנים בין שלבים.xlsx
@@ -83,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -100,6 +100,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1974,23 +1977,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>הסינון שבשימוש: 1.5 סטיות תקן, קנה מידה log, חוסם low. תצפית מחוץ לחלון אינה נספרת - לא בזמנים ולא בשיעור ההגעה.</t>
+          <t>השיטה: antimode. הרצפה נמצאת מצורת ההתפלגות - בליטה בימים הראשונים, שקע אחריה, ואז האוכלוסייה האמיתית - ונקבעת בשקע. תא בהיסטוגרמה 3 ימים, יחס בליטה לשקע 2.0. שלב שההתפלגות שלו חלקה אינו נחתך כלל. תצפית שנפסלה אינה נספרת לא בזמנים ולא בשיעור ההגעה.</t>
         </is>
       </c>
     </row>
@@ -2003,37 +2008,47 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>רצפת החלון (ימים)</t>
+          <t>רצפה שנמצאה (ימים)</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
+          <t>רצפת 1.5σ להשוואה</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
           <t>תצפיות לפני</t>
         </is>
       </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>נפסלו כמהיר מדי</t>
-        </is>
-      </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
+          <t>נפסלו</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
           <t>תצפיות אחרי</t>
         </is>
       </c>
-      <c r="F4" s="1" t="inlineStr">
-        <is>
-          <t>שיעור גיוס אחרי הסינון</t>
-        </is>
-      </c>
       <c r="G4" s="1" t="inlineStr">
         <is>
-          <t>חציון ימים אחרי</t>
+          <t>שיעור גיוס</t>
         </is>
       </c>
       <c r="H4" s="1" t="inlineStr">
         <is>
-          <t>ממוצע ימים אחרי</t>
+          <t>חציון ימים</t>
+        </is>
+      </c>
+      <c r="I4" s="1" t="inlineStr">
+        <is>
+          <t>ממוצע ימים</t>
+        </is>
+      </c>
+      <c r="J4" s="1" t="inlineStr">
+        <is>
+          <t>הנימוק</t>
         </is>
       </c>
     </row>
@@ -2044,25 +2059,33 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="C5" s="4" t="n">
         <v>4.6</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="D5" s="3" t="n">
         <v>1170</v>
       </c>
-      <c r="D5" s="3" t="n">
-        <v>181</v>
-      </c>
       <c r="E5" s="3" t="n">
-        <v>989</v>
-      </c>
-      <c r="F5" s="9" t="n">
-        <v>0.08397300000000001</v>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>79</v>
+        <v>262</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>908</v>
+      </c>
+      <c r="G5" s="9" t="n">
+        <v>0.07684199999999999</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>84.5</v>
+        <v>85</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>91.09999999999999</v>
+      </c>
+      <c r="J5" s="10" t="inlineStr">
+        <is>
+          <t>בליטה 118 בהתחלה, שקע 5 סביב יום 18, ואחריו 40</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -2071,26 +2094,36 @@
           <t>זימון למבחן מקוון</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>לא נמצאה</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n">
         <v>37.8</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="D6" s="3" t="n">
         <v>551</v>
       </c>
-      <c r="D6" s="3" t="n">
-        <v>34</v>
-      </c>
       <c r="E6" s="3" t="n">
-        <v>517</v>
-      </c>
-      <c r="F6" s="9" t="n">
-        <v>0.170064</v>
-      </c>
-      <c r="G6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>551</v>
+      </c>
+      <c r="G6" s="9" t="n">
+        <v>0.18138</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>86</v>
+      </c>
+      <c r="I6" s="4" t="n">
         <v>91</v>
       </c>
-      <c r="H6" s="4" t="n">
-        <v>95.3</v>
+      <c r="J6" s="10" t="inlineStr">
+        <is>
+          <t>אין בליטה בהתחלה: 1 מול שקע 0, פחות מפי 2.0</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -2100,25 +2133,33 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="C7" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="D7" s="3" t="n">
         <v>654</v>
       </c>
-      <c r="D7" s="3" t="n">
-        <v>39</v>
-      </c>
       <c r="E7" s="3" t="n">
-        <v>615</v>
-      </c>
-      <c r="F7" s="9" t="n">
-        <v>0.217876</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>69</v>
+        <v>24</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>630</v>
+      </c>
+      <c r="G7" s="9" t="n">
+        <v>0.223128</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>76.5</v>
+        <v>67.5</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="J7" s="10" t="inlineStr">
+        <is>
+          <t>בליטה 10 בהתחלה, שקע 2 סביב יום 12, ואחריו 37</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -2128,25 +2169,33 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" s="4" t="n">
         <v>18.4</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="D8" s="3" t="n">
         <v>897</v>
       </c>
-      <c r="D8" s="3" t="n">
-        <v>51</v>
-      </c>
       <c r="E8" s="3" t="n">
-        <v>846</v>
-      </c>
-      <c r="F8" s="9" t="n">
-        <v>0.398507</v>
-      </c>
-      <c r="G8" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>883</v>
+      </c>
+      <c r="G8" s="9" t="n">
+        <v>0.416064</v>
+      </c>
+      <c r="H8" s="4" t="n">
         <v>57</v>
       </c>
-      <c r="H8" s="4" t="n">
-        <v>65.59999999999999</v>
+      <c r="I8" s="4" t="n">
+        <v>63.4</v>
+      </c>
+      <c r="J8" s="10" t="inlineStr">
+        <is>
+          <t>בליטה 10 בהתחלה, שקע 4 סביב יום 3, ואחריו 65</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -2155,26 +2204,36 @@
           <t>מרכז הערכה</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>לא נמצאה</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="D9" s="3" t="n">
         <v>487</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="E9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>487</v>
+      </c>
+      <c r="G9" s="9" t="n">
+        <v>0.5021</v>
+      </c>
+      <c r="H9" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="E9" s="3" t="n">
-        <v>456</v>
-      </c>
-      <c r="F9" s="9" t="n">
-        <v>0.470669</v>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="H9" s="4" t="n">
-        <v>42.4</v>
+      <c r="I9" s="4" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="J9" s="10" t="inlineStr">
+        <is>
+          <t>אין בליטה בהתחלה: 4 מול שקע 5, פחות מפי 2.0</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -2183,33 +2242,44 @@
           <t>יחב"מ</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>לא נמצאה</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n">
         <v>2.4</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>1565</v>
       </c>
-      <c r="D10" s="3" t="n">
-        <v>150</v>
-      </c>
       <c r="E10" s="3" t="n">
-        <v>1415</v>
-      </c>
-      <c r="F10" s="9" t="n">
-        <v>0.704804</v>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>20</v>
+        <v>0</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>1565</v>
+      </c>
+      <c r="G10" s="9" t="n">
+        <v>0.775275</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>27.9</v>
+        <v>17</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="J10" s="10" t="inlineStr">
+        <is>
+          <t>אין בליטה בהתחלה: 173 מול שקע 97, פחות מפי 2.0</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>למה החלון מחושב על הלוג ולא על הימים עצמם: התפלגות זמנים חסומה באפס ומשתרעת ימינה. בקנה מידה רגיל, «ממוצע פחות 1.5 סטיות תקן» יוצא שלילי בחלק מהמעברים - ואז הוא אינו חוסם דבר בקצה המהיר, שהוא בדיוק הקצה שבו הבעיה. הגיליון הראשון מציג את שני החלונות זה לצד זה, והגבולות השליליים מסומנים שם בצהוב.
-למה נחסם רק הקצה המהיר: בקצה האיטי אין ממצא דומה, ולבדיקת קבצים נפסלות שם אפס תצפיות. חסימה דו-צדדית היתה מוחקת גיוסים איטיים אמיתיים בשלבים המאוחרים ומושכת את הזמן הממוצע כלפי מטה - כלומר גורמת למחשבון להבטיח גיוס מהיר מהמציאות.</t>
+          <t>למה סטיית תקן נפסלה כשיטת סינון: בבדיקת קבצים היא נותנת רצפה של 4.6 ימים בלבד, ומשאירה גיוסים תוך שבוע מבדיקת קבצים - שאינם אפשריים בתהליך הזה. הסיבה היא שהתפלגות זמנים חסומה באפס ומשתרעת ימינה, ולכן «ממוצע פחות 1.5 סטיות תקן» יוצא שלילי או נמוך מאוד דווקא במעברים הארוכים. עמודת «רצפת 1.5σ להשוואה» מציגה מה היא היתה נותנת, לצד הרצפה שנמצאה בפועל.
+למה נחתך רק הקצה המהיר: בקצה האיטי אין בליטה מלאכותית. חיתוך שם היה מוחק גיוסים איטיים אמיתיים ומושך את הזמן הממוצע כלפי מטה - כלומר גורם למחשבון להבטיח גיוס מהיר מהמציאות.
+שלב שכתוב בו «לא נמצאה» הוא שלב שההתפלגות שלו חלקה, בלי שתי אוכלוסיות, ולכן לא נחתך בו דבר. כך נשמר למשל המעבר מיחב"מ אל הגיוס, שבו גיוס תוך יומיים סביר לגמרי.</t>
         </is>
       </c>
     </row>
@@ -2222,8 +2292,8 @@
     <row r="20"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:H2"/>
-    <mergeCell ref="A13:H20"/>
+    <mergeCell ref="A13:J20"/>
+    <mergeCell ref="A1:J2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/קבצים/התקבל/זמנים בין שלבים.xlsx
+++ b/קבצים/התקבל/זמנים בין שלבים.xlsx
@@ -91,8 +91,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S26"/>
+  <dimension ref="A1:S33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -597,7 +597,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>בדיקת קבצים</t>
+          <t>הגשות</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -606,52 +606,52 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1647</v>
+        <v>716</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>66.09999999999999</v>
+        <v>102.1</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>46.8</v>
+        <v>40.9</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>64</v>
-      </c>
-      <c r="H2" s="5" t="n">
-        <v>-4.1</v>
+        <v>98</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>40.8</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>136.3</v>
-      </c>
-      <c r="J2" s="6" t="n">
-        <v>0.9222829386763813</v>
+        <v>163.4</v>
+      </c>
+      <c r="J2" s="5" t="n">
+        <v>0.86731843575419</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>5.1</v>
+        <v>46.6</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>277.8</v>
-      </c>
-      <c r="M2" s="6" t="n">
-        <v>0.8603521554341227</v>
-      </c>
-      <c r="N2" s="6" t="n">
-        <v>0.1396478445658774</v>
-      </c>
-      <c r="O2" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" s="6" t="n">
-        <v>0.08986035215543413</v>
-      </c>
-      <c r="Q2" s="6" t="n">
-        <v>0.1560412871888282</v>
+        <v>185.8</v>
+      </c>
+      <c r="M2" s="5" t="n">
+        <v>0.8924581005586593</v>
+      </c>
+      <c r="N2" s="5" t="n">
+        <v>0.07402234636871509</v>
+      </c>
+      <c r="O2" s="5" t="n">
+        <v>0.0335195530726257</v>
+      </c>
+      <c r="P2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="5" t="n">
+        <v>0.002793296089385475</v>
       </c>
       <c r="R2" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S2" s="4" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="3">
@@ -662,7 +662,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>זימון למבחן מקוון</t>
+          <t>בדיקת קבצים</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -671,49 +671,49 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>826</v>
+        <v>1674</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>82.59999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>36.6</v>
+        <v>46.9</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>77</v>
-      </c>
-      <c r="H3" s="4" t="n">
-        <v>27.8</v>
+        <v>63</v>
+      </c>
+      <c r="H3" s="6" t="n">
+        <v>-5.2</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>137.4</v>
-      </c>
-      <c r="J3" s="6" t="n">
-        <v>0.8753026634382567</v>
+        <v>135.6</v>
+      </c>
+      <c r="J3" s="5" t="n">
+        <v>0.9205495818399044</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>34.1</v>
+        <v>4.9</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>159.1</v>
-      </c>
-      <c r="M3" s="6" t="n">
-        <v>0.9031476997578692</v>
-      </c>
-      <c r="N3" s="6" t="n">
-        <v>0.06174334140435835</v>
-      </c>
-      <c r="O3" s="6" t="n">
-        <v>0.0351089588377724</v>
-      </c>
-      <c r="P3" s="6" t="n">
-        <v>0.002421307506053269</v>
-      </c>
-      <c r="Q3" s="6" t="n">
-        <v>0.004842615012106538</v>
+        <v>273.6</v>
+      </c>
+      <c r="M3" s="5" t="n">
+        <v>0.8614097968936678</v>
+      </c>
+      <c r="N3" s="5" t="n">
+        <v>0.1385902031063321</v>
+      </c>
+      <c r="O3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" s="5" t="n">
+        <v>0.08960573476702509</v>
+      </c>
+      <c r="Q3" s="5" t="n">
+        <v>0.1600955794504182</v>
       </c>
       <c r="R3" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S3" s="4" t="n">
         <v>225</v>
@@ -727,7 +727,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>יום מיון מקוון</t>
+          <t>זימון למבחן מקוון</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -736,52 +736,52 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>915</v>
+        <v>828</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>67.09999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>35.4</v>
+        <v>36.6</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>13.9</v>
+        <v>27.5</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>120.2</v>
-      </c>
-      <c r="J4" s="6" t="n">
-        <v>0.8819672131147541</v>
+        <v>137.4</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>0.8743961352657005</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>21</v>
+        <v>33.8</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>151.6</v>
-      </c>
-      <c r="M4" s="6" t="n">
-        <v>0.9114754098360656</v>
-      </c>
-      <c r="N4" s="6" t="n">
-        <v>0.06010928961748634</v>
-      </c>
-      <c r="O4" s="6" t="n">
-        <v>0.02841530054644809</v>
-      </c>
-      <c r="P4" s="6" t="n">
-        <v>0.00546448087431694</v>
-      </c>
-      <c r="Q4" s="6" t="n">
-        <v>0.01748633879781421</v>
+        <v>159.7</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>0.9094202898550725</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>0.05555555555555555</v>
+      </c>
+      <c r="O4" s="5" t="n">
+        <v>0.03502415458937198</v>
+      </c>
+      <c r="P4" s="5" t="n">
+        <v>0.002415458937198068</v>
+      </c>
+      <c r="Q4" s="5" t="n">
+        <v>0.004830917874396135</v>
       </c>
       <c r="R4" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S4" s="4" t="n">
-        <v>210</v>
+        <v>225</v>
       </c>
     </row>
     <row r="5">
@@ -792,7 +792,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>יום מיון</t>
+          <t>יום מיון מקוון</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -801,52 +801,52 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>1245</v>
+        <v>918</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>56.9</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>33</v>
+        <v>35.5</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>7.5</v>
+        <v>13.8</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>106.4</v>
-      </c>
-      <c r="J5" s="6" t="n">
-        <v>0.8963855421686747</v>
+        <v>120.1</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>0.8823529411764706</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>16.7</v>
+        <v>20.9</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>131.1</v>
-      </c>
-      <c r="M5" s="6" t="n">
-        <v>0.9060240963855422</v>
-      </c>
-      <c r="N5" s="6" t="n">
-        <v>0.05783132530120482</v>
-      </c>
-      <c r="O5" s="6" t="n">
-        <v>0.03614457831325301</v>
-      </c>
-      <c r="P5" s="6" t="n">
-        <v>0.01124497991967872</v>
-      </c>
-      <c r="Q5" s="6" t="n">
-        <v>0.02088353413654619</v>
+        <v>151.4</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>0.9106753812636166</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>0.06100217864923747</v>
+      </c>
+      <c r="O5" s="5" t="n">
+        <v>0.02832244008714597</v>
+      </c>
+      <c r="P5" s="5" t="n">
+        <v>0.005446623093681918</v>
+      </c>
+      <c r="Q5" s="5" t="n">
+        <v>0.01742919389978214</v>
       </c>
       <c r="R5" s="4" t="n">
         <v>0</v>
       </c>
       <c r="S5" s="4" t="n">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="6">
@@ -857,7 +857,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>מרכז הערכה</t>
+          <t>יום מיון</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -866,52 +866,52 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>553</v>
+        <v>1277</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>38.5</v>
+        <v>55.8</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>29.7</v>
+        <v>33.3</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="H6" s="5" t="n">
-        <v>-6</v>
+        <v>49</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>5.9</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>83.09999999999999</v>
-      </c>
-      <c r="J6" s="6" t="n">
-        <v>0.9150090415913201</v>
+        <v>105.8</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>0.8950665622552858</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>8.800000000000001</v>
+        <v>14.9</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>93.7</v>
-      </c>
-      <c r="M6" s="6" t="n">
-        <v>0.8716094032549728</v>
-      </c>
-      <c r="N6" s="6" t="n">
-        <v>0.06871609403254973</v>
-      </c>
-      <c r="O6" s="6" t="n">
-        <v>0.05967450271247739</v>
-      </c>
-      <c r="P6" s="6" t="n">
-        <v>0.009041591320072333</v>
-      </c>
-      <c r="Q6" s="6" t="n">
-        <v>0.0488245931283906</v>
+        <v>135.4</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>0.9177760375880971</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>0.0548159749412686</v>
+      </c>
+      <c r="O6" s="5" t="n">
+        <v>0.0274079874706343</v>
+      </c>
+      <c r="P6" s="5" t="n">
+        <v>0.01409553641346907</v>
+      </c>
+      <c r="Q6" s="5" t="n">
+        <v>0.02897415818324197</v>
       </c>
       <c r="R6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>184</v>
+        <v>204</v>
       </c>
     </row>
     <row r="7">
@@ -922,7 +922,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>יחב"מ</t>
+          <t>מרכז הערכה</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -931,117 +931,117 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>1753</v>
+        <v>587</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>24.7</v>
+        <v>37.1</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>24.5</v>
+        <v>29.5</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="H7" s="5" t="n">
-        <v>-12.1</v>
+        <v>29</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-7.1</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>61.4</v>
-      </c>
-      <c r="J7" s="6" t="n">
-        <v>0.930405019965773</v>
+        <v>81.3</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>0.9182282793867121</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>2.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>78.3</v>
-      </c>
-      <c r="M7" s="6" t="n">
-        <v>0.8613804905875642</v>
-      </c>
-      <c r="N7" s="6" t="n">
-        <v>0.1032515687393041</v>
-      </c>
-      <c r="O7" s="6" t="n">
-        <v>0.03536794067313177</v>
-      </c>
-      <c r="P7" s="6" t="n">
-        <v>0.1032515687393041</v>
-      </c>
-      <c r="Q7" s="6" t="n">
-        <v>0.2475755847119224</v>
+        <v>90.7</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>0.858603066439523</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>0.0817717206132879</v>
+      </c>
+      <c r="O7" s="5" t="n">
+        <v>0.05962521294718909</v>
+      </c>
+      <c r="P7" s="5" t="n">
+        <v>0.008517887563884156</v>
+      </c>
+      <c r="Q7" s="5" t="n">
+        <v>0.05792163543441227</v>
       </c>
       <c r="R7" s="4" t="n">
         <v>0</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>220</v>
+        <v>184</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>בין שלבים</t>
+          <t>עד גיוס</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>בדיקת קבצים</t>
+          <t>יחב"מ</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>זימון למבחן מקוון</t>
+          <t>גיוס</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>5135</v>
+        <v>1945</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>14.2</v>
+        <v>23.1</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>24.6</v>
+        <v>23.8</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="H8" s="5" t="n">
-        <v>-22.8</v>
+        <v>16</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-12.7</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>51.2</v>
-      </c>
-      <c r="J8" s="6" t="n">
-        <v>0.936319376825706</v>
+        <v>58.8</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>0.9280205655526992</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.3</v>
+        <v>2</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>47.2</v>
-      </c>
-      <c r="M8" s="6" t="n">
-        <v>0.9285296981499513</v>
-      </c>
-      <c r="N8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="6" t="n">
-        <v>0.07147030185004868</v>
-      </c>
-      <c r="P8" s="6" t="n">
-        <v>0.3933787731256086</v>
-      </c>
-      <c r="Q8" s="6" t="n">
-        <v>0.5887049659201558</v>
+        <v>72.59999999999999</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>0.8498714652956298</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>0.1110539845758355</v>
+      </c>
+      <c r="O8" s="5" t="n">
+        <v>0.0390745501285347</v>
+      </c>
+      <c r="P8" s="5" t="n">
+        <v>0.1110539845758355</v>
+      </c>
+      <c r="Q8" s="5" t="n">
+        <v>0.2760925449871465</v>
       </c>
       <c r="R8" s="4" t="n">
         <v>0</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>184</v>
+        <v>220</v>
       </c>
     </row>
     <row r="9">
@@ -1052,61 +1052,61 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
+          <t>הגשות</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
           <t>בדיקת קבצים</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>יום מיון מקוון</t>
-        </is>
-      </c>
       <c r="D9" s="3" t="n">
-        <v>3502</v>
+        <v>21208</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>36.7</v>
+        <v>8.5</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>36.1</v>
+        <v>21.8</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="H9" s="5" t="n">
-        <v>-17.5</v>
+        <v>2</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>-24.1</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>90.90000000000001</v>
-      </c>
-      <c r="J9" s="6" t="n">
-        <v>0.9037692747001713</v>
+        <v>41.1</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>0.9493587325537532</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>6</v>
+        <v>-0.4</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>95.5</v>
-      </c>
-      <c r="M9" s="6" t="n">
-        <v>0.8589377498572245</v>
-      </c>
-      <c r="N9" s="6" t="n">
-        <v>0.05025699600228441</v>
-      </c>
-      <c r="O9" s="6" t="n">
-        <v>0.09080525414049115</v>
-      </c>
-      <c r="P9" s="6" t="n">
-        <v>0.01342090234151913</v>
-      </c>
-      <c r="Q9" s="6" t="n">
-        <v>0.09794403198172473</v>
+        <v>20.9</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>0.9011222180309317</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="5" t="n">
+        <v>0.09887778196906828</v>
+      </c>
+      <c r="P9" s="5" t="n">
+        <v>0.5648340248962656</v>
+      </c>
+      <c r="Q9" s="5" t="n">
+        <v>0.8040833647680121</v>
       </c>
       <c r="R9" s="4" t="n">
         <v>0</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>189</v>
+        <v>217</v>
       </c>
     </row>
     <row r="10">
@@ -1117,61 +1117,61 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>בדיקת קבצים</t>
+          <t>הגשות</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>יום מיון</t>
+          <t>זימון למבחן מקוון</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>2797</v>
+        <v>5445</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>42.9</v>
+        <v>25.5</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>31.8</v>
+        <v>35.1</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="H10" s="5" t="n">
-        <v>-4.7</v>
+        <v>13</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-27.1</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>90.59999999999999</v>
-      </c>
-      <c r="J10" s="6" t="n">
-        <v>0.9031104755094744</v>
+        <v>78.09999999999999</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>0.9171717171717172</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>9.4</v>
+        <v>0.9</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>109.1</v>
-      </c>
-      <c r="M10" s="6" t="n">
-        <v>0.8848766535573829</v>
-      </c>
-      <c r="N10" s="6" t="n">
-        <v>0.06006435466571326</v>
-      </c>
-      <c r="O10" s="6" t="n">
-        <v>0.05505899177690383</v>
-      </c>
-      <c r="P10" s="6" t="n">
-        <v>0.01394351090454058</v>
-      </c>
-      <c r="Q10" s="6" t="n">
-        <v>0.03825527350732928</v>
+        <v>85.7</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>0.8672176308539945</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>0.05766758494031221</v>
+      </c>
+      <c r="O10" s="5" t="n">
+        <v>0.0751147842056933</v>
+      </c>
+      <c r="P10" s="5" t="n">
+        <v>0.173921028466483</v>
+      </c>
+      <c r="Q10" s="5" t="n">
+        <v>0.3757575757575757</v>
       </c>
       <c r="R10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>186</v>
+        <v>222</v>
       </c>
     </row>
     <row r="11">
@@ -1182,61 +1182,61 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>בדיקת קבצים</t>
+          <t>הגשות</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>מרכז הערכה</t>
+          <t>יום מיון מקוון</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>734</v>
+        <v>3573</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>68.90000000000001</v>
+        <v>47.1</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>29.9</v>
+        <v>39.7</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>65</v>
-      </c>
-      <c r="H11" s="4" t="n">
-        <v>24.1</v>
+        <v>34</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-12.5</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>113.7</v>
-      </c>
-      <c r="J11" s="6" t="n">
-        <v>0.8746594005449592</v>
+        <v>106.7</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>0.9017632241813602</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>29.2</v>
+        <v>10.2</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>131.1</v>
-      </c>
-      <c r="M11" s="6" t="n">
-        <v>0.9005449591280654</v>
-      </c>
-      <c r="N11" s="6" t="n">
-        <v>0.05722070844686648</v>
-      </c>
-      <c r="O11" s="6" t="n">
-        <v>0.04223433242506812</v>
-      </c>
-      <c r="P11" s="6" t="n">
-        <v>0.001362397820163488</v>
-      </c>
-      <c r="Q11" s="6" t="n">
-        <v>0.005449591280653951</v>
+        <v>113.8</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>0.8466274839070809</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>0.06465155331654072</v>
+      </c>
+      <c r="O11" s="5" t="n">
+        <v>0.08872096277637839</v>
+      </c>
+      <c r="P11" s="5" t="n">
+        <v>0.001959137979289113</v>
+      </c>
+      <c r="Q11" s="5" t="n">
+        <v>0.03470472991883571</v>
       </c>
       <c r="R11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>173</v>
+        <v>222</v>
       </c>
     </row>
     <row r="12">
@@ -1247,61 +1247,61 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>בדיקת קבצים</t>
+          <t>הגשות</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>יחב"מ</t>
+          <t>יום מיון</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1452</v>
+        <v>2662</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>58.3</v>
+        <v>58.9</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>36.2</v>
+        <v>39.1</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>3.9</v>
+        <v>0.3</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>112.6</v>
-      </c>
-      <c r="J12" s="6" t="n">
-        <v>0.8849862258953168</v>
+        <v>117.4</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>0.8966942148760331</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>10</v>
+        <v>17.4</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>179.8</v>
-      </c>
-      <c r="M12" s="6" t="n">
-        <v>0.9256198347107438</v>
-      </c>
-      <c r="N12" s="6" t="n">
-        <v>0.07369146005509641</v>
-      </c>
-      <c r="O12" s="6" t="n">
-        <v>0.0006887052341597796</v>
-      </c>
-      <c r="P12" s="6" t="n">
-        <v>0.02892561983471074</v>
-      </c>
-      <c r="Q12" s="6" t="n">
-        <v>0.05165289256198347</v>
+        <v>128.9</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>0.8636363636363636</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>0.06160781367392937</v>
+      </c>
+      <c r="O12" s="5" t="n">
+        <v>0.07475582268970699</v>
+      </c>
+      <c r="P12" s="5" t="n">
+        <v>0.0003756574004507889</v>
+      </c>
+      <c r="Q12" s="5" t="n">
+        <v>0.0067618332081142</v>
       </c>
       <c r="R12" s="4" t="n">
         <v>0</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>181</v>
+        <v>227</v>
       </c>
     </row>
     <row r="13">
@@ -1312,61 +1312,61 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>זימון למבחן מקוון</t>
+          <t>הגשות</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>יום מיון מקוון</t>
+          <t>מרכז הערכה</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>3313</v>
+        <v>761</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>19.1</v>
+        <v>86.2</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>18.9</v>
+        <v>38.8</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="H13" s="5" t="n">
-        <v>-9.300000000000001</v>
+        <v>78</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>28</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>47.5</v>
-      </c>
-      <c r="J13" s="6" t="n">
-        <v>0.9399335949290674</v>
+        <v>144.5</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>0.873850197109067</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>3.9</v>
+        <v>38.1</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>45.1</v>
-      </c>
-      <c r="M13" s="6" t="n">
-        <v>0.8853003320253546</v>
-      </c>
-      <c r="N13" s="6" t="n">
-        <v>0.04889827950498038</v>
-      </c>
-      <c r="O13" s="6" t="n">
-        <v>0.06580138846966496</v>
-      </c>
-      <c r="P13" s="6" t="n">
-        <v>0.02837307576214911</v>
-      </c>
-      <c r="Q13" s="6" t="n">
-        <v>0.2324177482644129</v>
+        <v>158.5</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>0.8672798948751642</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>0.06044678055190539</v>
+      </c>
+      <c r="O13" s="5" t="n">
+        <v>0.07227332457293036</v>
+      </c>
+      <c r="P13" s="5" t="n">
+        <v>0.001314060446780552</v>
+      </c>
+      <c r="Q13" s="5" t="n">
+        <v>0.001314060446780552</v>
       </c>
       <c r="R13" s="4" t="n">
         <v>0</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>169</v>
+        <v>221</v>
       </c>
     </row>
     <row r="14">
@@ -1377,61 +1377,61 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>זימון למבחן מקוון</t>
+          <t>הגשות</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>יום מיון</t>
+          <t>יחב"מ</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>2425</v>
+        <v>1075</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>34.9</v>
+        <v>86.3</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>26.4</v>
+        <v>40.8</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="H14" s="5" t="n">
-        <v>-4.7</v>
+        <v>80</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>25.1</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="J14" s="6" t="n">
-        <v>0.9154639175257732</v>
+        <v>147.5</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>0.8706976744186047</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>9.199999999999999</v>
+        <v>32.1</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>79.7</v>
-      </c>
-      <c r="M14" s="6" t="n">
-        <v>0.8585567010309278</v>
-      </c>
-      <c r="N14" s="6" t="n">
-        <v>0.06639175257731959</v>
-      </c>
-      <c r="O14" s="6" t="n">
-        <v>0.07505154639175257</v>
-      </c>
-      <c r="P14" s="6" t="n">
-        <v>0.00577319587628866</v>
-      </c>
-      <c r="Q14" s="6" t="n">
-        <v>0.04288659793814433</v>
+        <v>176.9</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>0.9013953488372093</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>0.06697674418604652</v>
+      </c>
+      <c r="O14" s="5" t="n">
+        <v>0.03162790697674418</v>
+      </c>
+      <c r="P14" s="5" t="n">
+        <v>0.00186046511627907</v>
+      </c>
+      <c r="Q14" s="5" t="n">
+        <v>0.005581395348837209</v>
       </c>
       <c r="R14" s="4" t="n">
         <v>0</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>181</v>
+        <v>220</v>
       </c>
     </row>
     <row r="15">
@@ -1442,61 +1442,61 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
+          <t>בדיקת קבצים</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
           <t>זימון למבחן מקוון</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>מרכז הערכה</t>
-        </is>
-      </c>
       <c r="D15" s="3" t="n">
-        <v>648</v>
+        <v>6055</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>61.9</v>
+        <v>16.3</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>25.7</v>
+        <v>29.5</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>58</v>
-      </c>
-      <c r="H15" s="4" t="n">
-        <v>23.4</v>
+        <v>6</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>-28</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>100.5</v>
-      </c>
-      <c r="J15" s="6" t="n">
-        <v>0.8811728395061729</v>
+        <v>60.6</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>0.9327828241123038</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>27.7</v>
+        <v>-0.3</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>113.7</v>
-      </c>
-      <c r="M15" s="6" t="n">
-        <v>0.9012345679012346</v>
-      </c>
-      <c r="N15" s="6" t="n">
-        <v>0.05555555555555555</v>
-      </c>
-      <c r="O15" s="6" t="n">
-        <v>0.04320987654320987</v>
-      </c>
-      <c r="P15" s="6" t="n">
-        <v>0.00154320987654321</v>
-      </c>
-      <c r="Q15" s="6" t="n">
-        <v>0.006172839506172839</v>
+        <v>53.7</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>0.9250206440957887</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="5" t="n">
+        <v>0.0749793559042114</v>
+      </c>
+      <c r="P15" s="5" t="n">
+        <v>0.3800165152766309</v>
+      </c>
+      <c r="Q15" s="5" t="n">
+        <v>0.5725846407927333</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>185</v>
+        <v>221</v>
       </c>
     </row>
     <row r="16">
@@ -1507,61 +1507,61 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>זימון למבחן מקוון</t>
+          <t>בדיקת קבצים</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>יחב"מ</t>
+          <t>יום מיון מקוון</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>932</v>
+        <v>4205</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>64</v>
+        <v>38.1</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>29.7</v>
+        <v>38.1</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>59</v>
-      </c>
-      <c r="H16" s="4" t="n">
-        <v>19.3</v>
+        <v>25</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-19</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>108.6</v>
-      </c>
-      <c r="J16" s="6" t="n">
-        <v>0.8626609442060086</v>
+        <v>95.3</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>0.9046373365041617</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>24.6</v>
+        <v>6.1</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>128.3</v>
-      </c>
-      <c r="M16" s="6" t="n">
-        <v>0.9141630901287554</v>
-      </c>
-      <c r="N16" s="6" t="n">
-        <v>0.05686695278969957</v>
-      </c>
-      <c r="O16" s="6" t="n">
-        <v>0.02896995708154506</v>
-      </c>
-      <c r="P16" s="6" t="n">
-        <v>0.002145922746781116</v>
-      </c>
-      <c r="Q16" s="6" t="n">
-        <v>0.01180257510729614</v>
+        <v>99.40000000000001</v>
+      </c>
+      <c r="M16" s="5" t="n">
+        <v>0.8475624256837099</v>
+      </c>
+      <c r="N16" s="5" t="n">
+        <v>0.06278240190249702</v>
+      </c>
+      <c r="O16" s="5" t="n">
+        <v>0.0896551724137931</v>
+      </c>
+      <c r="P16" s="5" t="n">
+        <v>0.01212841854934602</v>
+      </c>
+      <c r="Q16" s="5" t="n">
+        <v>0.09678953626634959</v>
       </c>
       <c r="R16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>171</v>
+        <v>218</v>
       </c>
     </row>
     <row r="17">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>יום מיון מקוון</t>
+          <t>בדיקת קבצים</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1581,52 +1581,52 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>2398</v>
+        <v>3475</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>19.7</v>
+        <v>44.4</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>24.1</v>
+        <v>34.8</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="H17" s="5" t="n">
-        <v>-16.5</v>
+        <v>34</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-7.8</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>55.8</v>
-      </c>
-      <c r="J17" s="6" t="n">
-        <v>0.932443703085905</v>
+        <v>96.59999999999999</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>0.9073381294964029</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1.3</v>
+        <v>9.5</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>64.59999999999999</v>
-      </c>
-      <c r="M17" s="6" t="n">
-        <v>0.8386155129274395</v>
-      </c>
-      <c r="N17" s="6" t="n">
-        <v>0.103419516263553</v>
-      </c>
-      <c r="O17" s="6" t="n">
-        <v>0.0579649708090075</v>
-      </c>
-      <c r="P17" s="6" t="n">
-        <v>0.1255212677231026</v>
-      </c>
-      <c r="Q17" s="6" t="n">
-        <v>0.3023352793994996</v>
+        <v>112.3</v>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>0.8797122302158273</v>
+      </c>
+      <c r="N17" s="5" t="n">
+        <v>0.05899280575539569</v>
+      </c>
+      <c r="O17" s="5" t="n">
+        <v>0.06129496402877698</v>
+      </c>
+      <c r="P17" s="5" t="n">
+        <v>0.01237410071942446</v>
+      </c>
+      <c r="Q17" s="5" t="n">
+        <v>0.0362589928057554</v>
       </c>
       <c r="R17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>189</v>
+        <v>225</v>
       </c>
     </row>
     <row r="18">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>יום מיון מקוון</t>
+          <t>בדיקת קבצים</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1646,52 +1646,52 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>734</v>
+        <v>958</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>46.2</v>
+        <v>75.2</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>25.8</v>
+        <v>35.8</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>7.5</v>
+        <v>21.5</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>85</v>
-      </c>
-      <c r="J18" s="6" t="n">
-        <v>0.9073569482288828</v>
+        <v>129</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>0.8924843423799582</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>14.2</v>
+        <v>30.7</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>104.4</v>
-      </c>
-      <c r="M18" s="6" t="n">
-        <v>0.9046321525885559</v>
-      </c>
-      <c r="N18" s="6" t="n">
-        <v>0.05449591280653951</v>
-      </c>
-      <c r="O18" s="6" t="n">
-        <v>0.04087193460490463</v>
-      </c>
-      <c r="P18" s="6" t="n">
-        <v>0.009536784741144414</v>
-      </c>
-      <c r="Q18" s="6" t="n">
-        <v>0.02316076294277929</v>
+        <v>145</v>
+      </c>
+      <c r="M18" s="5" t="n">
+        <v>0.8883089770354906</v>
+      </c>
+      <c r="N18" s="5" t="n">
+        <v>0.05427974947807934</v>
+      </c>
+      <c r="O18" s="5" t="n">
+        <v>0.05741127348643006</v>
+      </c>
+      <c r="P18" s="5" t="n">
+        <v>0.00104384133611691</v>
+      </c>
+      <c r="Q18" s="5" t="n">
+        <v>0.004175365344467641</v>
       </c>
       <c r="R18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>165</v>
+        <v>223</v>
       </c>
     </row>
     <row r="19">
@@ -1702,7 +1702,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>יום מיון מקוון</t>
+          <t>בדיקת קבצים</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1711,52 +1711,52 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>981</v>
+        <v>1870</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>50.5</v>
+        <v>63.2</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>28.9</v>
+        <v>40.5</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>7.2</v>
+        <v>2.4</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>93.8</v>
-      </c>
-      <c r="J19" s="6" t="n">
-        <v>0.8786952089704383</v>
+        <v>124</v>
+      </c>
+      <c r="J19" s="5" t="n">
+        <v>0.8893048128342246</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>13.8</v>
+        <v>11.2</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>121.9</v>
-      </c>
-      <c r="M19" s="6" t="n">
-        <v>0.9164118246687054</v>
-      </c>
-      <c r="N19" s="6" t="n">
-        <v>0.05300713557594292</v>
-      </c>
-      <c r="O19" s="6" t="n">
-        <v>0.03058103975535168</v>
-      </c>
-      <c r="P19" s="6" t="n">
-        <v>0.0163098878695209</v>
-      </c>
-      <c r="Q19" s="6" t="n">
-        <v>0.03363914373088685</v>
+        <v>190.7</v>
+      </c>
+      <c r="M19" s="5" t="n">
+        <v>0.9208556149732621</v>
+      </c>
+      <c r="N19" s="5" t="n">
+        <v>0.07219251336898395</v>
+      </c>
+      <c r="O19" s="5" t="n">
+        <v>0.006951871657754011</v>
+      </c>
+      <c r="P19" s="5" t="n">
+        <v>0.02406417112299465</v>
+      </c>
+      <c r="Q19" s="5" t="n">
+        <v>0.04652406417112299</v>
       </c>
       <c r="R19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>167</v>
+        <v>220</v>
       </c>
     </row>
     <row r="20">
@@ -1767,61 +1767,61 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>יום מיון</t>
+          <t>זימון למבחן מקוון</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>מרכז הערכה</t>
+          <t>יום מיון מקוון</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>978</v>
+        <v>3977</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>32.8</v>
+        <v>19.4</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>20.5</v>
+        <v>19.6</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="H20" s="4" t="n">
-        <v>2</v>
+        <v>14</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-10</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>63.6</v>
-      </c>
-      <c r="J20" s="6" t="n">
-        <v>0.9335378323108384</v>
+        <v>48.9</v>
+      </c>
+      <c r="J20" s="5" t="n">
+        <v>0.9411616796580337</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>11.5</v>
+        <v>3.9</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>66.2</v>
-      </c>
-      <c r="M20" s="6" t="n">
-        <v>0.8834355828220859</v>
-      </c>
-      <c r="N20" s="6" t="n">
-        <v>0.06032719836400818</v>
-      </c>
-      <c r="O20" s="6" t="n">
-        <v>0.05623721881390593</v>
-      </c>
-      <c r="P20" s="6" t="n">
-        <v>0.002044989775051125</v>
-      </c>
-      <c r="Q20" s="6" t="n">
-        <v>0.016359918200409</v>
+        <v>46.1</v>
+      </c>
+      <c r="M20" s="5" t="n">
+        <v>0.8873522755846115</v>
+      </c>
+      <c r="N20" s="5" t="n">
+        <v>0.04953482524515967</v>
+      </c>
+      <c r="O20" s="5" t="n">
+        <v>0.06311289917022882</v>
+      </c>
+      <c r="P20" s="5" t="n">
+        <v>0.02816193110384712</v>
+      </c>
+      <c r="Q20" s="5" t="n">
+        <v>0.2323359316067387</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>154</v>
+        <v>209</v>
       </c>
     </row>
     <row r="21">
@@ -1832,61 +1832,61 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
+          <t>זימון למבחן מקוון</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
           <t>יום מיון</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>יחב"מ</t>
-        </is>
-      </c>
       <c r="D21" s="3" t="n">
-        <v>1367</v>
+        <v>3002</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>35.9</v>
+        <v>34.3</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>24.4</v>
+        <v>27</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="H21" s="5" t="n">
-        <v>-0.7</v>
+        <v>27</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>-6.2</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>72.5</v>
-      </c>
-      <c r="J21" s="6" t="n">
-        <v>0.9326993416239941</v>
+        <v>74.7</v>
+      </c>
+      <c r="J21" s="5" t="n">
+        <v>0.9213857428381079</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>82.7</v>
-      </c>
-      <c r="M21" s="6" t="n">
-        <v>0.8873445501097293</v>
-      </c>
-      <c r="N21" s="6" t="n">
-        <v>0.06437454279444038</v>
-      </c>
-      <c r="O21" s="6" t="n">
-        <v>0.04828090709583029</v>
-      </c>
-      <c r="P21" s="6" t="n">
-        <v>0.008046817849305048</v>
-      </c>
-      <c r="Q21" s="6" t="n">
-        <v>0.04681784930504755</v>
+        <v>78.5</v>
+      </c>
+      <c r="M21" s="5" t="n">
+        <v>0.871419053964024</v>
+      </c>
+      <c r="N21" s="5" t="n">
+        <v>0.05796135909393738</v>
+      </c>
+      <c r="O21" s="5" t="n">
+        <v>0.07061958694203864</v>
+      </c>
+      <c r="P21" s="5" t="n">
+        <v>0.006662225183211193</v>
+      </c>
+      <c r="Q21" s="5" t="n">
+        <v>0.04263824117255163</v>
       </c>
       <c r="R21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>186</v>
+        <v>215</v>
       </c>
     </row>
     <row r="22">
@@ -1897,75 +1897,530 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
+          <t>זימון למבחן מקוון</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
           <t>מרכז הערכה</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="D22" s="3" t="n">
+        <v>839</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>63</v>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>112.8</v>
+      </c>
+      <c r="J22" s="5" t="n">
+        <v>0.8986889153754469</v>
+      </c>
+      <c r="K22" s="4" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="L22" s="4" t="n">
+        <v>126.6</v>
+      </c>
+      <c r="M22" s="5" t="n">
+        <v>0.9046483909415971</v>
+      </c>
+      <c r="N22" s="5" t="n">
+        <v>0.05244338498212157</v>
+      </c>
+      <c r="O22" s="5" t="n">
+        <v>0.04290822407628129</v>
+      </c>
+      <c r="P22" s="5" t="n">
+        <v>0.001191895113230036</v>
+      </c>
+      <c r="Q22" s="5" t="n">
+        <v>0.007151370679380214</v>
+      </c>
+      <c r="R22" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="S22" s="4" t="n">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>בין שלבים</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>זימון למבחן מקוון</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>יחב"מ</t>
         </is>
       </c>
-      <c r="D22" s="3" t="n">
-        <v>592</v>
-      </c>
-      <c r="E22" s="4" t="n">
+      <c r="D23" s="3" t="n">
+        <v>1197</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>67.3</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>62</v>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>117.2</v>
+      </c>
+      <c r="J23" s="5" t="n">
+        <v>0.8813700918964077</v>
+      </c>
+      <c r="K23" s="4" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="L23" s="4" t="n">
+        <v>135.1</v>
+      </c>
+      <c r="M23" s="5" t="n">
+        <v>0.9005847953216374</v>
+      </c>
+      <c r="N23" s="5" t="n">
+        <v>0.05764411027568922</v>
+      </c>
+      <c r="O23" s="5" t="n">
+        <v>0.04177109440267335</v>
+      </c>
+      <c r="P23" s="5" t="n">
+        <v>0.001670843776106934</v>
+      </c>
+      <c r="Q23" s="5" t="n">
+        <v>0.009189640768588136</v>
+      </c>
+      <c r="R23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" s="4" t="n">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>בין שלבים</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>יום מיון מקוון</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>יום מיון</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>2935</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>-17.8</v>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="J24" s="5" t="n">
+        <v>0.9376490630323679</v>
+      </c>
+      <c r="K24" s="4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L24" s="4" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="M24" s="5" t="n">
+        <v>0.8419080068143101</v>
+      </c>
+      <c r="N24" s="5" t="n">
+        <v>0.1001703577512777</v>
+      </c>
+      <c r="O24" s="5" t="n">
+        <v>0.05792163543441227</v>
+      </c>
+      <c r="P24" s="5" t="n">
+        <v>0.1298126064735945</v>
+      </c>
+      <c r="Q24" s="5" t="n">
+        <v>0.3396933560477002</v>
+      </c>
+      <c r="R24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" s="4" t="n">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>בין שלבים</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>יום מיון מקוון</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>מרכז הערכה</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>918</v>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I25" s="4" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="J25" s="5" t="n">
+        <v>0.9161220043572985</v>
+      </c>
+      <c r="K25" s="4" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="L25" s="4" t="n">
+        <v>112</v>
+      </c>
+      <c r="M25" s="5" t="n">
+        <v>0.8943355119825708</v>
+      </c>
+      <c r="N25" s="5" t="n">
+        <v>0.05773420479302832</v>
+      </c>
+      <c r="O25" s="5" t="n">
+        <v>0.04793028322440087</v>
+      </c>
+      <c r="P25" s="5" t="n">
+        <v>0.007625272331154684</v>
+      </c>
+      <c r="Q25" s="5" t="n">
+        <v>0.01851851851851852</v>
+      </c>
+      <c r="R25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" s="4" t="n">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>בין שלבים</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>יום מיון מקוון</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>יחב"מ</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>1221</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>47</v>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I26" s="4" t="n">
+        <v>101.8</v>
+      </c>
+      <c r="J26" s="5" t="n">
+        <v>0.9009009009009009</v>
+      </c>
+      <c r="K26" s="4" t="n">
         <v>15.1</v>
       </c>
-      <c r="F22" s="4" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="G22" s="4" t="n">
+      <c r="L26" s="4" t="n">
+        <v>126.2</v>
+      </c>
+      <c r="M26" s="5" t="n">
+        <v>0.9058149058149059</v>
+      </c>
+      <c r="N26" s="5" t="n">
+        <v>0.05487305487305488</v>
+      </c>
+      <c r="O26" s="5" t="n">
+        <v>0.03931203931203931</v>
+      </c>
+      <c r="P26" s="5" t="n">
+        <v>0.0131040131040131</v>
+      </c>
+      <c r="Q26" s="5" t="n">
+        <v>0.02702702702702703</v>
+      </c>
+      <c r="R26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" s="4" t="n">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>בין שלבים</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>יום מיון</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>מרכז הערכה</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>1210</v>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="H27" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I27" s="4" t="n">
+        <v>68.09999999999999</v>
+      </c>
+      <c r="J27" s="5" t="n">
+        <v>0.9355371900826446</v>
+      </c>
+      <c r="K27" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="L27" s="4" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="M27" s="5" t="n">
+        <v>0.8793388429752066</v>
+      </c>
+      <c r="N27" s="5" t="n">
+        <v>0.06446280991735537</v>
+      </c>
+      <c r="O27" s="5" t="n">
+        <v>0.05619834710743802</v>
+      </c>
+      <c r="P27" s="5" t="n">
+        <v>0.001652892561983471</v>
+      </c>
+      <c r="Q27" s="5" t="n">
+        <v>0.0140495867768595</v>
+      </c>
+      <c r="R27" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S27" s="4" t="n">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>בין שלבים</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>יום מיון</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>יחב"מ</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>1699</v>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="H28" s="6" t="n">
+        <v>-3.8</v>
+      </c>
+      <c r="I28" s="4" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="J28" s="5" t="n">
+        <v>0.9323131253678635</v>
+      </c>
+      <c r="K28" s="4" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="L28" s="4" t="n">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="M28" s="5" t="n">
+        <v>0.8846380223660977</v>
+      </c>
+      <c r="N28" s="5" t="n">
+        <v>0.06003531489111242</v>
+      </c>
+      <c r="O28" s="5" t="n">
+        <v>0.05532666274278988</v>
+      </c>
+      <c r="P28" s="5" t="n">
+        <v>0.0100058858151854</v>
+      </c>
+      <c r="Q28" s="5" t="n">
+        <v>0.04473219540906415</v>
+      </c>
+      <c r="R28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" s="4" t="n">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>בין שלבים</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>מרכז הערכה</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>יחב"מ</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>719</v>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="G29" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="H22" s="5" t="n">
-        <v>-8.300000000000001</v>
-      </c>
-      <c r="I22" s="4" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="J22" s="6" t="n">
-        <v>0.9375</v>
-      </c>
-      <c r="K22" s="4" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="L22" s="4" t="n">
-        <v>37.4</v>
-      </c>
-      <c r="M22" s="6" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="N22" s="6" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="O22" s="6" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P22" s="6" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="Q22" s="6" t="n">
-        <v>0.3209459459459459</v>
-      </c>
-      <c r="R22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" s="4" t="n">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="H29" s="6" t="n">
+        <v>-15</v>
+      </c>
+      <c r="I29" s="4" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="J29" s="5" t="n">
+        <v>0.9401947148817803</v>
+      </c>
+      <c r="K29" s="4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L29" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="M29" s="5" t="n">
+        <v>0.8692628650904033</v>
+      </c>
+      <c r="N29" s="5" t="n">
+        <v>0.06258692628650904</v>
+      </c>
+      <c r="O29" s="5" t="n">
+        <v>0.06815020862308763</v>
+      </c>
+      <c r="P29" s="5" t="n">
+        <v>0.06258692628650904</v>
+      </c>
+      <c r="Q29" s="5" t="n">
+        <v>0.3310152990264256</v>
+      </c>
+      <c r="R29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" s="4" t="n">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>«מינימום 1.5σ» מסומן בצהוב כשהוא יוצא שלילי. במקרים האלה החלון הרגיל אינו חוסם דבר בקצה המהיר, כי אין ימים שליליים. לכן מוצג גם חלון על הלוג, שהוא הצורה הנכונה לחסום התפלגות זמנים משני הצדדים.</t>
         </is>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26"/>
+    <row r="32"/>
+    <row r="33"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A24:S26"/>
+    <mergeCell ref="A31:S33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1977,7 +2432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2055,227 +2510,265 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>בדיקת קבצים</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n">
-        <v>21</v>
+          <t>הגשות</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>לא נמצאה</t>
+        </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>4.6</v>
+        <v>52.8</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>1170</v>
+        <v>391</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>262</v>
+        <v>0</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>908</v>
+        <v>391</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>0.07684199999999999</v>
+        <v>0.032057</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>91.09999999999999</v>
+        <v>112.9</v>
       </c>
       <c r="J5" s="10" t="inlineStr">
         <is>
-          <t>בליטה 118 בהתחלה, שקע 5 סביב יום 18, ואחריו 40</t>
+          <t>אין בליטה בהתחלה: 1 מול שקע 0, פחות מפי 2.0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>זימון למבחן מקוון</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>לא נמצאה</t>
-        </is>
+          <t>בדיקת קבצים</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>21</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>37.8</v>
+        <v>4.6</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>551</v>
+        <v>1170</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>0</v>
+        <v>262</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>551</v>
+        <v>908</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>0.18138</v>
+        <v>0.07684199999999999</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>91</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="J6" s="10" t="inlineStr">
         <is>
-          <t>אין בליטה בהתחלה: 1 מול שקע 0, פחות מפי 2.0</t>
+          <t>בליטה 118 בהתחלה, שקע 5 סביב יום 18, ואחריו 40</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>יום מיון מקוון</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>15</v>
+          <t>זימון למבחן מקוון</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>לא נמצאה</t>
+        </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>22</v>
+        <v>37.8</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>654</v>
+        <v>551</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>630</v>
+        <v>551</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>0.223128</v>
+        <v>0.18138</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>67.5</v>
+        <v>86</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>75.09999999999999</v>
+        <v>91</v>
       </c>
       <c r="J7" s="10" t="inlineStr">
         <is>
-          <t>בליטה 10 בהתחלה, שקע 2 סביב יום 12, ואחריו 37</t>
+          <t>אין בליטה בהתחלה: 1 מול שקע 0, פחות מפי 2.0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>יום מיון</t>
+          <t>יום מיון מקוון</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>18.4</v>
+        <v>22</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>897</v>
+        <v>654</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>883</v>
+        <v>630</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>0.416064</v>
+        <v>0.223128</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>57</v>
+        <v>67.5</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>63.4</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="J8" s="10" t="inlineStr">
         <is>
-          <t>בליטה 10 בהתחלה, שקע 4 סביב יום 3, ואחריו 65</t>
+          <t>בליטה 10 בהתחלה, שקע 2 סביב יום 12, ואחריו 37</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>מרכז הערכה</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>לא נמצאה</t>
-        </is>
+          <t>יום מיון</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>6</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>9</v>
+        <v>18.4</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>487</v>
+        <v>897</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>487</v>
+        <v>883</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>0.5021</v>
+        <v>0.416064</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>40.1</v>
+        <v>63.4</v>
       </c>
       <c r="J9" s="10" t="inlineStr">
         <is>
-          <t>אין בליטה בהתחלה: 4 מול שקע 5, פחות מפי 2.0</t>
+          <t>בליטה 10 בהתחלה, שקע 4 סביב יום 3, ואחריו 65</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>מרכז הערכה</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>לא נמצאה</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>487</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>487</v>
+      </c>
+      <c r="G10" s="9" t="n">
+        <v>0.5021</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="J10" s="10" t="inlineStr">
+        <is>
+          <t>אין בליטה בהתחלה: 4 מול שקע 5, פחות מפי 2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
           <t>יחב"מ</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>לא נמצאה</t>
         </is>
       </c>
-      <c r="C10" s="4" t="n">
+      <c r="C11" s="4" t="n">
         <v>2.4</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>1565</v>
       </c>
-      <c r="E10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="3" t="n">
+      <c r="E11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3" t="n">
         <v>1565</v>
       </c>
-      <c r="G10" s="9" t="n">
+      <c r="G11" s="9" t="n">
         <v>0.775275</v>
       </c>
-      <c r="H10" s="4" t="n">
+      <c r="H11" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="I10" s="4" t="n">
+      <c r="I11" s="4" t="n">
         <v>25.3</v>
       </c>
-      <c r="J10" s="10" t="inlineStr">
+      <c r="J11" s="10" t="inlineStr">
         <is>
           <t>אין בליטה בהתחלה: 173 מול שקע 97, פחות מפי 2.0</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>למה סטיית תקן נפסלה כשיטת סינון: בבדיקת קבצים היא נותנת רצפה של 4.6 ימים בלבד, ומשאירה גיוסים תוך שבוע מבדיקת קבצים - שאינם אפשריים בתהליך הזה. הסיבה היא שהתפלגות זמנים חסומה באפס ומשתרעת ימינה, ולכן «ממוצע פחות 1.5 סטיות תקן» יוצא שלילי או נמוך מאוד דווקא במעברים הארוכים. עמודת «רצפת 1.5σ להשוואה» מציגה מה היא היתה נותנת, לצד הרצפה שנמצאה בפועל.
 למה נחתך רק הקצה המהיר: בקצה האיטי אין בליטה מלאכותית. חיתוך שם היה מוחק גיוסים איטיים אמיתיים ומושך את הזמן הממוצע כלפי מטה - כלומר גורם למחשבון להבטיח גיוס מהיר מהמציאות.
@@ -2283,16 +2776,16 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15"/>
     <row r="16"/>
     <row r="17"/>
     <row r="18"/>
     <row r="19"/>
     <row r="20"/>
+    <row r="21"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A13:J20"/>
+    <mergeCell ref="A14:J21"/>
     <mergeCell ref="A1:J2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
